--- a/data/excel/api_test_data.xlsx
+++ b/data/excel/api_test_data.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="29">
   <si>
     <t>用例描述</t>
   </si>
@@ -37,6 +37,9 @@
     <t>测试body</t>
   </si>
   <si>
+    <t>预期结果</t>
+  </si>
+  <si>
     <t>用例是否执行</t>
   </si>
   <si>
@@ -44,6 +47,19 @@
   </si>
   <si>
     <t>{"username":"testuser001","email":"testuser001@example.com","password":"Test@123456"}</t>
+  </si>
+  <si>
+    <t>{
+    "number": "1",
+    "code": 0,
+    "status": 1,
+    "data": {
+        "userId": "${notnull}"
+    },
+    "message": "请求成功",
+    "ok": true,
+    "msg": "请求成功"
+}</t>
   </si>
   <si>
     <t>TRUE</t>
@@ -122,14 +138,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -585,153 +594,159 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1078,67 +1093,73 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="2"/>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="23.0973451327434" customWidth="1"/>
-    <col min="2" max="2" width="88.0796460176991" customWidth="1"/>
-    <col min="3" max="3" width="11.4867256637168" customWidth="1"/>
+    <col min="2" max="3" width="88.0796460176991" customWidth="1"/>
+    <col min="4" max="4" width="11.4867256637168" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:4">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="2" s="1" customFormat="1" ht="148.5" spans="1:4">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="C2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
+    <row r="3" s="1" customFormat="1" spans="1:4">
+      <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
+    <row r="4" s="1" customFormat="1" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C4" t="s">
-        <v>8</v>
-      </c>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
-        <v>8</v>
+    <row r="5" s="1" customFormat="1" spans="1:4">
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1166,51 +1187,51 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1238,40 +1259,40 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/data/excel/api_test_data.xlsx
+++ b/data/excel/api_test_data.xlsx
@@ -71,13 +71,13 @@
     <t>{"username":"admin","email":"admin@example.com","password":"Test@123456"}</t>
   </si>
   <si>
+    <t>注册用户-邮箱格式错误</t>
+  </si>
+  <si>
+    <t>{"username":"testuser002","email":"invalid-email","password":"Test@123456"}</t>
+  </si>
+  <si>
     <t>FALSE</t>
-  </si>
-  <si>
-    <t>注册用户-邮箱格式错误</t>
-  </si>
-  <si>
-    <t>{"username":"testuser002","email":"invalid-email","password":"Test@123456"}</t>
   </si>
   <si>
     <t>注册用户-密码长度不足</t>
@@ -1137,18 +1137,18 @@
         <v>9</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:4">
       <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:4">
@@ -1159,7 +1159,7 @@
         <v>14</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1231,7 +1231,7 @@
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
